--- a/data/trans_camb/P16A07-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A07-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,64</t>
+          <t>0,08; 3,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,86</t>
+          <t>-0,74; 1,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,7</t>
+          <t>0,57; 3,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,9</t>
+          <t>-4,38; 1,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,84</t>
+          <t>-2,66; 3,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,17</t>
+          <t>-2,18; 3,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,37</t>
+          <t>-1,13; 2,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,15</t>
+          <t>-1,08; 1,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,87</t>
+          <t>0,17; 3,17</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,55; 1406,66</t>
+          <t>-34,85; 1373,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-78,71; 701,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,81; 1453,89</t>
+          <t>10,28; 1319,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-75,31; 104,78</t>
+          <t>-79,75; 83,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 130,29</t>
+          <t>-53,79; 151,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,54; 155,03</t>
+          <t>-40,86; 142,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 178,0</t>
+          <t>-46,66; 174,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 149,91</t>
+          <t>-45,94; 146,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 235,49</t>
+          <t>0,43; 234,23</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,99</t>
+          <t>-0,67; 4,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,32</t>
+          <t>-2,13; 1,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,43</t>
+          <t>-0,72; 3,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 1,29</t>
+          <t>-5,42; 1,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; -0,01</t>
+          <t>-6,62; -0,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 2,54</t>
+          <t>-3,71; 2,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,75</t>
+          <t>-2,55; 1,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -0,03</t>
+          <t>-3,64; 0,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,11</t>
+          <t>-1,91; 2,08</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 524,81</t>
+          <t>-39,53; 600,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,65; 208,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,82; 437,24</t>
+          <t>-37,77; 495,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-70,4; 28,78</t>
+          <t>-66,78; 28,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,71; 3,55</t>
+          <t>-80,63; -0,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,22; 59,55</t>
+          <t>-44,47; 54,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,68; 58,44</t>
+          <t>-51,96; 59,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,36; 5,7</t>
+          <t>-71,51; 13,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,01; 77,06</t>
+          <t>-35,59; 73,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 4,15</t>
+          <t>-0,2; 4,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,31</t>
+          <t>-1,68; 2,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 3,27</t>
+          <t>-2,71; 3,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 8,08</t>
+          <t>-2,79; 8,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 10,09</t>
+          <t>-2,88; 10,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 6,86</t>
+          <t>-4,26; 6,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 4,48</t>
+          <t>0,05; 4,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,63</t>
+          <t>-0,85; 3,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 3,45</t>
+          <t>-3,13; 3,42</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 273,06</t>
+          <t>-8,58; 261,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 146,24</t>
+          <t>-48,1; 145,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,57; 154,48</t>
+          <t>-66,09; 175,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 192,18</t>
+          <t>-29,75; 202,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 214,47</t>
+          <t>-36,17; 226,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 149,18</t>
+          <t>-39,76; 144,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 163,34</t>
+          <t>-0,03; 184,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 138,83</t>
+          <t>-19,56; 138,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,7; 106,66</t>
+          <t>-53,83; 111,29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,1</t>
+          <t>0,38; 3,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,71</t>
+          <t>-0,61; 1,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,03</t>
+          <t>0,4; 3,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,13</t>
+          <t>-1,31; 3,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,3</t>
+          <t>-3,34; 1,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 2,97</t>
+          <t>-3,85; 2,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,99</t>
+          <t>0,34; 2,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,26</t>
+          <t>-1,21; 1,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,65</t>
+          <t>-0,31; 2,62</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,36; 204,5</t>
+          <t>12,68; 211,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,38; 113,96</t>
+          <t>-27,2; 113,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,11; 206,31</t>
+          <t>12,33; 203,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 81,47</t>
+          <t>-17,08; 80,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,17; 25,44</t>
+          <t>-44,77; 27,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,31; 54,4</t>
+          <t>-49,68; 56,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,44; 98,6</t>
+          <t>6,16; 96,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 42,2</t>
+          <t>-29,0; 39,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 85,49</t>
+          <t>-5,62; 87,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,24</t>
+          <t>-3,5; 1,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,31</t>
+          <t>-3,53; 1,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 3,21</t>
+          <t>-2,36; 3,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 7,92</t>
+          <t>1,01; 7,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 6,59</t>
+          <t>-0,5; 6,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,87</t>
+          <t>-2,3; 4,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,23</t>
+          <t>-0,2; 4,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,24</t>
+          <t>-1,29; 3,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,85</t>
+          <t>-1,25; 3,03</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,41; 65,33</t>
+          <t>-70,74; 68,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-64,27; 73,77</t>
+          <t>-67,07; 79,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,85; 167,77</t>
+          <t>-44,05; 159,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9,43; 123,87</t>
+          <t>10,09; 113,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 104,66</t>
+          <t>-5,52; 98,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 58,44</t>
+          <t>-23,26; 63,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 80,07</t>
+          <t>-4,65; 84,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 63,01</t>
+          <t>-17,06; 56,86</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 56,74</t>
+          <t>-16,91; 59,2</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,37; -0,9</t>
+          <t>-5,56; -0,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,17</t>
+          <t>-4,84; 0,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,81</t>
+          <t>-3,88; 1,7</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,2; 4,51</t>
+          <t>-0,04; 4,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,43</t>
+          <t>-0,73; 3,44</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,53</t>
+          <t>-0,74; 3,5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,09</t>
+          <t>-0,56; 3,03</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,27</t>
+          <t>-1,32; 2,4</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,37</t>
+          <t>-1,31; 2,45</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 32,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 41,5</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-84,64; 151,94</t>
+          <t>-83,95; 116,65</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1,42; 78,65</t>
+          <t>-0,82; 81,62</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 61,74</t>
+          <t>-10,36; 63,91</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 61,18</t>
+          <t>-10,56; 63,84</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 62,74</t>
+          <t>-9,69; 59,21</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 46,16</t>
+          <t>-20,58; 48,69</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 46,32</t>
+          <t>-19,84; 50,2</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,74</t>
+          <t>0,14; 1,76</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,77</t>
+          <t>-0,59; 0,79</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,96</t>
+          <t>0,15; 1,87</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,14</t>
+          <t>0,72; 3,13</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,96</t>
+          <t>-0,58; 1,86</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,9</t>
+          <t>-0,79; 1,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,2</t>
+          <t>0,7; 2,22</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,08</t>
+          <t>-0,32; 1,08</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>-0,06; 1,72</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>6,29; 95,0</t>
+          <t>4,87; 95,93</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-28,84; 42,94</t>
+          <t>-25,23; 44,88</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7,82; 109,07</t>
+          <t>7,81; 100,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,98; 53,45</t>
+          <t>10,17; 52,36</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 33,02</t>
+          <t>-8,53; 31,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 32,28</t>
+          <t>-10,87; 33,03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,38; 54,82</t>
+          <t>14,07; 54,94</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 26,86</t>
+          <t>-7,15; 27,17</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,06; 40,13</t>
+          <t>-1,29; 43,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A07-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A07-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,5</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,81</t>
+          <t>0,11; 3,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,91</t>
+          <t>-0,73; 1,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,85</t>
+          <t>0,53; 3,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 1,65</t>
+          <t>-4,07; 2,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 3,33</t>
+          <t>-3,32; 3,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,13</t>
+          <t>-2,67; 3,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,24</t>
+          <t>-0,99; 2,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,94</t>
+          <t>-1,01; 1,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,17</t>
+          <t>0,02; 2,86</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>262,1%</t>
+          <t>245,28%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,85; 1373,12</t>
+          <t>-14,47; 1331,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,5; 751,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 1319,63</t>
+          <t>5,31; 1276,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-79,75; 83,62</t>
+          <t>-75,83; 106,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,79; 151,56</t>
+          <t>-62,27; 139,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,86; 142,28</t>
+          <t>-43,02; 151,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 174,99</t>
+          <t>-41,73; 180,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,94; 146,43</t>
+          <t>-39,4; 150,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 234,23</t>
+          <t>-2,25; 229,13</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,23</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,4</t>
+          <t>-0,79; 3,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,33</t>
+          <t>-2,02; 1,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,39</t>
+          <t>-0,88; 3,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 1,13</t>
+          <t>-5,63; 1,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,62; -0,2</t>
+          <t>-6,57; -0,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 2,41</t>
+          <t>-3,59; 2,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,71</t>
+          <t>-2,59; 1,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,22</t>
+          <t>-3,71; -0,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,08</t>
+          <t>-1,83; 2,09</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-7,5%</t>
+          <t>-7,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,53; 600,59</t>
+          <t>-42,9; 548,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,73; 221,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,77; 495,86</t>
+          <t>-43,01; 409,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,78; 28,75</t>
+          <t>-70,09; 27,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,63; -0,69</t>
+          <t>-79,97; -2,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,47; 54,43</t>
+          <t>-43,59; 60,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,96; 59,58</t>
+          <t>-51,77; 57,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,51; 13,14</t>
+          <t>-72,06; 2,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 73,51</t>
+          <t>-35,38; 70,92</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>2,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 4,01</t>
+          <t>-0,44; 3,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,45</t>
+          <t>-1,54; 2,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,56</t>
+          <t>-0,15; 4,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 8,22</t>
+          <t>-2,92; 8,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 10,07</t>
+          <t>-2,66; 10,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 6,85</t>
+          <t>-4,12; 6,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,52</t>
+          <t>0,01; 4,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,73</t>
+          <t>-0,87; 3,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,42</t>
+          <t>-0,17; 4,23</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 261,22</t>
+          <t>-18,78; 238,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 145,56</t>
+          <t>-46,21; 158,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,09; 175,49</t>
+          <t>-10,64; 291,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,75; 202,62</t>
+          <t>-29,34; 179,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,17; 226,03</t>
+          <t>-31,12; 210,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 144,98</t>
+          <t>-40,1; 148,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 184,51</t>
+          <t>-1,81; 156,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 138,12</t>
+          <t>-21,16; 129,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,83; 111,29</t>
+          <t>-6,04; 154,96</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>2,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,29</t>
+          <t>0,36; 3,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,68</t>
+          <t>-0,61; 1,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,05</t>
+          <t>0,45; 3,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,86</t>
+          <t>-1,22; 4,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,39</t>
+          <t>-3,19; 1,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,99</t>
+          <t>-0,72; 4,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,95</t>
+          <t>0,36; 3,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,19</t>
+          <t>-1,23; 1,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,62</t>
+          <t>0,8; 3,23</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,68; 211,97</t>
+          <t>11,74; 205,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 113,52</t>
+          <t>-26,12; 115,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,33; 203,83</t>
+          <t>12,97; 186,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 80,15</t>
+          <t>-17,34; 81,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 27,37</t>
+          <t>-42,74; 32,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 56,89</t>
+          <t>-9,75; 85,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,16; 96,48</t>
+          <t>8,58; 100,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 39,89</t>
+          <t>-28,62; 38,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 87,24</t>
+          <t>18,09; 104,09</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,41</t>
+          <t>-3,71; 1,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,53</t>
+          <t>-3,49; 1,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 3,13</t>
+          <t>-2,61; 2,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,51</t>
+          <t>0,59; 7,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 6,34</t>
+          <t>-0,18; 6,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 4,19</t>
+          <t>-1,07; 4,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 4,33</t>
+          <t>-0,23; 4,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,04</t>
+          <t>-1,3; 2,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,03</t>
+          <t>-0,75; 3,13</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-70,74; 68,17</t>
+          <t>-69,97; 52,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-67,07; 79,74</t>
+          <t>-64,51; 77,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-44,05; 159,44</t>
+          <t>-48,25; 119,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,09; 113,78</t>
+          <t>4,76; 112,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 98,85</t>
+          <t>-2,28; 94,38</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 63,97</t>
+          <t>-11,54; 72,04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 84,51</t>
+          <t>-3,52; 84,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 56,86</t>
+          <t>-17,57; 56,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 59,2</t>
+          <t>-10,57; 61,39</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,74</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,56; -0,96</t>
+          <t>-5,41; -0,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 0,09</t>
+          <t>-4,76; 0,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,7</t>
+          <t>-3,09; 3,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 4,37</t>
+          <t>0,08; 4,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,44</t>
+          <t>-0,86; 3,32</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,5</t>
+          <t>-0,9; 3,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,03</t>
+          <t>-0,62; 2,91</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,4</t>
+          <t>-1,3; 2,55</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,45</t>
+          <t>-1,03; 2,53</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-38,76%</t>
+          <t>-14,91%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,14 +1835,14 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>18,64%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
           <t>22,05%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>22,05%</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>8,68%</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 8,5</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 41,5</t>
+          <t>-100,0; 22,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-83,95; 116,65</t>
+          <t>-75,89; 205,04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 81,62</t>
+          <t>1,03; 80,33</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 63,91</t>
+          <t>-11,81; 59,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 63,84</t>
+          <t>-12,66; 57,74</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 59,21</t>
+          <t>-8,52; 59,79</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 48,69</t>
+          <t>-19,6; 52,99</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 50,2</t>
+          <t>-15,88; 51,7</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>1,31</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,76</t>
+          <t>0,14; 1,83</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,79</t>
+          <t>-0,59; 0,78</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,87</t>
+          <t>0,55; 2,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,13</t>
+          <t>0,69; 3,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,86</t>
+          <t>-0,57; 2,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,92</t>
+          <t>0,15; 2,37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,22</t>
+          <t>0,64; 2,27</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,08</t>
+          <t>-0,37; 1,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,72</t>
+          <t>0,61; 1,99</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>4,87; 95,93</t>
+          <t>5,47; 101,3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 44,88</t>
+          <t>-24,89; 43,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7,81; 100,57</t>
+          <t>21,46; 124,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,17; 52,36</t>
+          <t>9,72; 55,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 31,79</t>
+          <t>-7,56; 34,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 33,03</t>
+          <t>2,04; 40,87</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,07; 54,94</t>
+          <t>13,22; 57,36</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 27,17</t>
+          <t>-8,05; 27,45</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 43,43</t>
+          <t>12,64; 50,54</t>
         </is>
       </c>
     </row>
